--- a/試験項目書兼結果報告書/試験項目書兼結果報告書_部品在庫照会API.xlsx
+++ b/試験項目書兼結果報告書/試験項目書兼結果報告書_部品在庫照会API.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="14055"/>
+    <workbookView windowWidth="19815" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="試験項目" sheetId="13" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="障害ID_001" sheetId="14" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">正常系!$A$1:$AX$388</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">正常系!$A$1:$AX$393</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">試験項目!$A$1:$T$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">不具合報告!$A$1:$K$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">異常系!$A$1:$AX$204</definedName>
@@ -208,13 +208,13 @@
     <t>ヘッダー：
   Authorization: Bearer &lt;有効JWT&gt;
 クエリパラメータ：
-　stock_id=1,3
+　stock_id=1,2
 　amount_min=150
 　amount_max=150</t>
   </si>
   <si>
     <t>ステータス：200
-返却されたレコードの部品在庫テーブル「stock_id」が必ず「1」または「3」であること
+返却されたレコードの部品在庫テーブル「stock_id」が必ず「1」または「2」であること
 返却され各レコードの部品在庫テーブル「amount」が「150」であること</t>
   </si>
   <si>
@@ -464,10 +464,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -521,14 +521,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -536,23 +528,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -575,22 +567,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -608,6 +599,22 @@
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -629,9 +636,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -646,13 +653,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -691,7 +691,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -709,78 +799,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -793,7 +811,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,25 +829,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -835,25 +853,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1037,21 +1037,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -1086,6 +1071,21 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1138,148 +1138,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1928,13 +1928,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>287020</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>240665</xdr:rowOff>
+      <xdr:rowOff>226060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>115570</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>135890</xdr:rowOff>
+      <xdr:rowOff>121285</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1951,7 +1951,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="287020" y="26788745"/>
+          <a:off x="287020" y="26774140"/>
           <a:ext cx="13973175" cy="8829675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2510,57 +2510,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>325</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>348</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="図形 35"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="314325" y="82962750"/>
-          <a:ext cx="14097000" cy="6000750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>355</xdr:row>
+      <xdr:row>360</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>355</xdr:row>
+      <xdr:row>360</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2577,7 +2535,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3143250" y="90620850"/>
+          <a:off x="3143250" y="91897200"/>
           <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2595,13 +2553,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>354</xdr:row>
+      <xdr:row>359</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>358</xdr:row>
+      <xdr:row>363</xdr:row>
       <xdr:rowOff>140970</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2619,7 +2577,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="314325" y="90365580"/>
+          <a:off x="314325" y="91641930"/>
           <a:ext cx="7781925" cy="1162050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2637,18 +2595,2747 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>361</xdr:row>
+      <xdr:row>366</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>385</xdr:row>
+      <xdr:row>390</xdr:row>
       <xdr:rowOff>169545</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="39" name="図形 38"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="314325" y="93428820"/>
+          <a:ext cx="14001750" cy="6296025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>50165</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>36830</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>240665</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="フレーム 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1238250" y="21748115"/>
+          <a:ext cx="1627505" cy="445770"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>191770</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>212725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>95885</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="フレーム 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="191770" y="23952835"/>
+          <a:ext cx="3361690" cy="447040"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>198755</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>163830</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>229870</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="フレーム 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5111750" y="1985645"/>
+          <a:ext cx="709930" cy="1307465"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>232410</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>172085</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>299085</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>109220</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="フレーム 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="232410" y="25699085"/>
+          <a:ext cx="1638300" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>287020</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>199390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="フレーム 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1229995" y="34916110"/>
+          <a:ext cx="1421765" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>192405</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>299085</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>204470</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="フレーム 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="192405" y="37174170"/>
+          <a:ext cx="7964805" cy="299720"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>300990</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>186690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>149860</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>149225</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="フレーム 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="300990" y="38987730"/>
+          <a:ext cx="4878070" cy="217805"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>81915</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>104140</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>163830</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>40640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="フレーム 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="710565" y="46563280"/>
+          <a:ext cx="2596515" cy="447040"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>299085</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>187325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>81280</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>173355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="フレーム 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1870710" y="45114845"/>
+          <a:ext cx="2296795" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 12672"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>271145</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>49530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>149225</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>245110</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="フレーム 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1842770" y="31958280"/>
+          <a:ext cx="2392680" cy="195580"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>186690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>149225</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="フレーム 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1746885" y="33627060"/>
+          <a:ext cx="2488565" cy="205740"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>300355</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>185420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>189865</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>191770</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="フレーム 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="300355" y="48941990"/>
+          <a:ext cx="7747635" cy="261620"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>109855</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>216535</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="フレーム 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1367155" y="56949340"/>
+          <a:ext cx="1421765" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>160655</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>231140</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>78740</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="フレーム 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="260350" y="59128025"/>
+          <a:ext cx="7828915" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>109855</xdr:colOff>
+      <xdr:row>269</xdr:row>
+      <xdr:rowOff>200660</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>271</xdr:row>
+      <xdr:rowOff>137795</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="フレーム 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1367155" y="68868290"/>
+          <a:ext cx="1421765" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>191770</xdr:colOff>
+      <xdr:row>278</xdr:row>
+      <xdr:rowOff>173355</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>54610</xdr:colOff>
+      <xdr:row>279</xdr:row>
+      <xdr:rowOff>151130</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="フレーム 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="191770" y="71138415"/>
+          <a:ext cx="8035290" cy="233045"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>245745</xdr:colOff>
+      <xdr:row>385</xdr:row>
+      <xdr:rowOff>159385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>109855</xdr:colOff>
+      <xdr:row>387</xdr:row>
+      <xdr:rowOff>96520</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="フレーム 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1817370" y="98438335"/>
+          <a:ext cx="2693035" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>325</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>353</xdr:row>
+      <xdr:rowOff>196215</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="図形 50"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2661,8 +5348,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="314325" y="92152470"/>
-          <a:ext cx="14001750" cy="6296025"/>
+          <a:off x="314325" y="82962750"/>
+          <a:ext cx="14030325" cy="7343775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2673,6 +5360,170 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>320</xdr:row>
+      <xdr:rowOff>159385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>321</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="フレーム 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="205740" y="81845785"/>
+          <a:ext cx="8035290" cy="233045"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3056,6 +5907,2630 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>179705</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>207645</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>46355</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>130810</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="フレーム 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3637280" y="1483995"/>
+          <a:ext cx="1123950" cy="433705"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>59690</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>234315</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>116205</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="フレーム 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5088890" y="2531745"/>
+          <a:ext cx="999490" cy="434340"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>78740</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>214630</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>220980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="フレーム 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4479290" y="7545705"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>259715</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>108585</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="フレーム 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5153025" y="9220200"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>157480</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>232410</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>293370</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>55245</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="フレーム 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4558030" y="13506450"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>60325</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>121285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>196215</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>199390</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="フレーム 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5089525" y="15182215"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>41275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>57785</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>174625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="フレーム 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4502150" y="19697065"/>
+          <a:ext cx="2156460" cy="388620"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>100965</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>153670</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>293370</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="フレーム 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="729615" y="22362160"/>
+          <a:ext cx="5221605" cy="631190"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>89535</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>210185</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>225425</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>33020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="フレーム 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4490085" y="25737185"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>226060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>189230</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>48895</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="フレーム 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5082540" y="28050490"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>85090</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>93980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="フレーム 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4485640" y="31924625"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>52070</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>217170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>187960</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>40005</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="フレーム 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5081270" y="33912810"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>104140</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>67945</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>240030</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="フレーム 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3247390" y="38103175"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>103505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>160655</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="フレーム 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="428625" y="38904545"/>
+          <a:ext cx="675005" cy="2494915"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>234315</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>198755</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>168275</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>43180</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="フレーム 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6835140" y="45381545"/>
+          <a:ext cx="3391535" cy="610235"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>78105</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="フレーム 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2660650" y="49267110"/>
+          <a:ext cx="1078865" cy="333375"/>
+        </a:xfrm>
+        <a:prstGeom prst="frame">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 6648"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="ja-JP">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4434,7 +9909,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AW388"/>
+  <dimension ref="A1:AW393"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="16384" width="3.66666666666667" style="5"/>
@@ -4752,7 +10227,6 @@
       <c r="O8" s="36"/>
       <c r="P8" s="36"/>
       <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
       <c r="S8" s="49"/>
       <c r="T8" s="49"/>
       <c r="U8" s="49"/>
@@ -13409,59 +18883,16 @@
       <c r="AW350" s="54"/>
     </row>
     <row r="351" customHeight="1" spans="1:49">
-      <c r="A351" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B351" s="37"/>
-      <c r="C351" s="37"/>
-      <c r="D351" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E351" s="38"/>
-      <c r="F351" s="38"/>
-      <c r="G351" s="39"/>
-      <c r="H351" s="39"/>
-      <c r="I351" s="39"/>
-      <c r="J351" s="47"/>
-      <c r="K351" s="47"/>
-      <c r="L351" s="47"/>
-      <c r="M351" s="47"/>
-      <c r="N351" s="47"/>
-      <c r="O351" s="47"/>
-      <c r="P351" s="47"/>
-      <c r="Q351" s="47"/>
-      <c r="R351" s="47"/>
-      <c r="S351" s="47"/>
-      <c r="T351" s="47"/>
-      <c r="U351" s="47"/>
-      <c r="V351" s="47"/>
-      <c r="W351" s="47"/>
-      <c r="X351" s="47"/>
-      <c r="Y351" s="47"/>
-      <c r="Z351" s="47"/>
-      <c r="AA351" s="47"/>
-      <c r="AB351" s="47"/>
-      <c r="AC351" s="47"/>
-      <c r="AD351" s="47"/>
-      <c r="AE351" s="47"/>
-      <c r="AF351" s="47"/>
-      <c r="AG351" s="47"/>
-      <c r="AH351" s="47"/>
-      <c r="AI351" s="47"/>
-      <c r="AJ351" s="47"/>
-      <c r="AK351" s="47"/>
-      <c r="AL351" s="47"/>
-      <c r="AM351" s="47"/>
-      <c r="AN351" s="47"/>
-      <c r="AO351" s="47"/>
-      <c r="AP351" s="47"/>
-      <c r="AQ351" s="47"/>
-      <c r="AR351" s="47"/>
-      <c r="AS351" s="47"/>
-      <c r="AT351" s="47"/>
-      <c r="AU351" s="47"/>
-      <c r="AV351" s="47"/>
-      <c r="AW351" s="53"/>
+      <c r="A351" s="40"/>
+      <c r="B351" s="41"/>
+      <c r="C351" s="41"/>
+      <c r="D351" s="42"/>
+      <c r="E351" s="42"/>
+      <c r="F351" s="42"/>
+      <c r="G351" s="43"/>
+      <c r="H351" s="43"/>
+      <c r="I351" s="43"/>
+      <c r="AW351" s="54"/>
     </row>
     <row r="352" customHeight="1" spans="1:49">
       <c r="A352" s="40"/>
@@ -13476,266 +18907,112 @@
       <c r="AW352" s="54"/>
     </row>
     <row r="353" customHeight="1" spans="1:49">
-      <c r="A353" s="5" t="s">
+      <c r="A353" s="40"/>
+      <c r="B353" s="41"/>
+      <c r="C353" s="41"/>
+      <c r="D353" s="42"/>
+      <c r="E353" s="42"/>
+      <c r="F353" s="42"/>
+      <c r="G353" s="43"/>
+      <c r="H353" s="43"/>
+      <c r="I353" s="43"/>
+      <c r="AW353" s="54"/>
+    </row>
+    <row r="354" customHeight="1" spans="1:49">
+      <c r="A354" s="40"/>
+      <c r="B354" s="41"/>
+      <c r="C354" s="41"/>
+      <c r="D354" s="42"/>
+      <c r="E354" s="42"/>
+      <c r="F354" s="42"/>
+      <c r="G354" s="43"/>
+      <c r="H354" s="43"/>
+      <c r="I354" s="43"/>
+      <c r="AW354" s="54"/>
+    </row>
+    <row r="355" customHeight="1" spans="1:49">
+      <c r="A355" s="40"/>
+      <c r="B355" s="41"/>
+      <c r="C355" s="41"/>
+      <c r="D355" s="42"/>
+      <c r="E355" s="42"/>
+      <c r="F355" s="42"/>
+      <c r="G355" s="43"/>
+      <c r="H355" s="43"/>
+      <c r="I355" s="43"/>
+      <c r="AW355" s="54"/>
+    </row>
+    <row r="356" customHeight="1" spans="1:49">
+      <c r="A356" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B356" s="37"/>
+      <c r="C356" s="37"/>
+      <c r="D356" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E356" s="38"/>
+      <c r="F356" s="38"/>
+      <c r="G356" s="39"/>
+      <c r="H356" s="39"/>
+      <c r="I356" s="39"/>
+      <c r="J356" s="47"/>
+      <c r="K356" s="47"/>
+      <c r="L356" s="47"/>
+      <c r="M356" s="47"/>
+      <c r="N356" s="47"/>
+      <c r="O356" s="47"/>
+      <c r="P356" s="47"/>
+      <c r="Q356" s="47"/>
+      <c r="R356" s="47"/>
+      <c r="S356" s="47"/>
+      <c r="T356" s="47"/>
+      <c r="U356" s="47"/>
+      <c r="V356" s="47"/>
+      <c r="W356" s="47"/>
+      <c r="X356" s="47"/>
+      <c r="Y356" s="47"/>
+      <c r="Z356" s="47"/>
+      <c r="AA356" s="47"/>
+      <c r="AB356" s="47"/>
+      <c r="AC356" s="47"/>
+      <c r="AD356" s="47"/>
+      <c r="AE356" s="47"/>
+      <c r="AF356" s="47"/>
+      <c r="AG356" s="47"/>
+      <c r="AH356" s="47"/>
+      <c r="AI356" s="47"/>
+      <c r="AJ356" s="47"/>
+      <c r="AK356" s="47"/>
+      <c r="AL356" s="47"/>
+      <c r="AM356" s="47"/>
+      <c r="AN356" s="47"/>
+      <c r="AO356" s="47"/>
+      <c r="AP356" s="47"/>
+      <c r="AQ356" s="47"/>
+      <c r="AR356" s="47"/>
+      <c r="AS356" s="47"/>
+      <c r="AT356" s="47"/>
+      <c r="AU356" s="47"/>
+      <c r="AV356" s="47"/>
+      <c r="AW356" s="53"/>
+    </row>
+    <row r="357" customHeight="1" spans="1:49">
+      <c r="A357" s="40"/>
+      <c r="B357" s="41"/>
+      <c r="C357" s="41"/>
+      <c r="D357" s="42"/>
+      <c r="E357" s="42"/>
+      <c r="F357" s="42"/>
+      <c r="G357" s="43"/>
+      <c r="H357" s="43"/>
+      <c r="I357" s="43"/>
+      <c r="AW357" s="54"/>
+    </row>
+    <row r="358" customHeight="1" spans="1:49">
+      <c r="A358" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C353" s="36"/>
-      <c r="D353" s="36"/>
-      <c r="E353" s="36"/>
-      <c r="F353" s="36"/>
-      <c r="G353" s="36"/>
-      <c r="H353" s="36"/>
-      <c r="I353" s="36"/>
-      <c r="J353" s="36"/>
-      <c r="K353" s="36"/>
-      <c r="L353" s="36"/>
-      <c r="M353" s="36"/>
-      <c r="N353" s="36"/>
-      <c r="O353" s="36"/>
-      <c r="P353" s="36"/>
-      <c r="Q353" s="36"/>
-      <c r="R353" s="36"/>
-      <c r="S353" s="49"/>
-      <c r="T353" s="49"/>
-      <c r="U353" s="49"/>
-      <c r="V353" s="49"/>
-      <c r="W353" s="36"/>
-      <c r="X353" s="36"/>
-      <c r="Y353" s="36"/>
-      <c r="Z353" s="36"/>
-      <c r="AA353" s="36"/>
-      <c r="AB353" s="36"/>
-      <c r="AC353" s="36"/>
-      <c r="AD353" s="36"/>
-      <c r="AE353" s="36"/>
-      <c r="AF353" s="36"/>
-      <c r="AG353" s="36"/>
-      <c r="AH353" s="36"/>
-      <c r="AI353" s="36"/>
-      <c r="AJ353" s="36"/>
-      <c r="AK353" s="36"/>
-      <c r="AL353" s="36"/>
-      <c r="AM353" s="36"/>
-      <c r="AN353" s="36"/>
-      <c r="AO353" s="36"/>
-      <c r="AP353" s="36"/>
-      <c r="AQ353" s="36"/>
-      <c r="AR353" s="36"/>
-      <c r="AS353" s="36"/>
-      <c r="AT353" s="36"/>
-      <c r="AU353" s="36"/>
-      <c r="AV353" s="36"/>
-      <c r="AW353" s="52"/>
-    </row>
-    <row r="354" customHeight="1" spans="1:49">
-      <c r="A354" s="35"/>
-      <c r="B354" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C354" s="36"/>
-      <c r="D354" s="36"/>
-      <c r="E354" s="36"/>
-      <c r="F354" s="36"/>
-      <c r="G354" s="36"/>
-      <c r="H354" s="36"/>
-      <c r="I354" s="36"/>
-      <c r="J354" s="36"/>
-      <c r="K354" s="36"/>
-      <c r="L354" s="36"/>
-      <c r="M354" s="36"/>
-      <c r="N354" s="36"/>
-      <c r="O354" s="36"/>
-      <c r="P354" s="36"/>
-      <c r="Q354" s="36"/>
-      <c r="R354" s="36"/>
-      <c r="S354" s="49"/>
-      <c r="T354" s="49"/>
-      <c r="U354" s="49"/>
-      <c r="V354" s="49"/>
-      <c r="W354" s="36"/>
-      <c r="X354" s="36"/>
-      <c r="Y354" s="36"/>
-      <c r="Z354" s="36"/>
-      <c r="AA354" s="36"/>
-      <c r="AB354" s="36"/>
-      <c r="AC354" s="36"/>
-      <c r="AD354" s="36"/>
-      <c r="AE354" s="36"/>
-      <c r="AF354" s="36"/>
-      <c r="AG354" s="36"/>
-      <c r="AH354" s="36"/>
-      <c r="AI354" s="36"/>
-      <c r="AJ354" s="36"/>
-      <c r="AK354" s="36"/>
-      <c r="AL354" s="36"/>
-      <c r="AM354" s="36"/>
-      <c r="AN354" s="36"/>
-      <c r="AO354" s="36"/>
-      <c r="AP354" s="36"/>
-      <c r="AQ354" s="36"/>
-      <c r="AR354" s="36"/>
-      <c r="AS354" s="36"/>
-      <c r="AT354" s="36"/>
-      <c r="AU354" s="36"/>
-      <c r="AV354" s="36"/>
-      <c r="AW354" s="52"/>
-    </row>
-    <row r="355" customHeight="1" spans="1:49">
-      <c r="A355" s="35"/>
-      <c r="B355" s="36"/>
-      <c r="C355" s="36"/>
-      <c r="D355" s="36"/>
-      <c r="E355" s="36"/>
-      <c r="F355" s="36"/>
-      <c r="G355" s="36"/>
-      <c r="H355" s="36"/>
-      <c r="I355" s="36"/>
-      <c r="J355" s="36"/>
-      <c r="K355" s="36"/>
-      <c r="L355" s="36"/>
-      <c r="M355" s="36"/>
-      <c r="N355" s="36"/>
-      <c r="O355" s="36"/>
-      <c r="P355" s="36"/>
-      <c r="Q355" s="36"/>
-      <c r="R355" s="36"/>
-      <c r="S355" s="49"/>
-      <c r="T355" s="49"/>
-      <c r="U355" s="49"/>
-      <c r="V355" s="49"/>
-      <c r="W355" s="36"/>
-      <c r="X355" s="36"/>
-      <c r="Y355" s="36"/>
-      <c r="Z355" s="36"/>
-      <c r="AA355" s="36"/>
-      <c r="AB355" s="36"/>
-      <c r="AC355" s="36"/>
-      <c r="AD355" s="36"/>
-      <c r="AE355" s="36"/>
-      <c r="AF355" s="36"/>
-      <c r="AG355" s="36"/>
-      <c r="AH355" s="36"/>
-      <c r="AI355" s="36"/>
-      <c r="AJ355" s="36"/>
-      <c r="AK355" s="36"/>
-      <c r="AL355" s="36"/>
-      <c r="AM355" s="36"/>
-      <c r="AN355" s="36"/>
-      <c r="AO355" s="36"/>
-      <c r="AP355" s="36"/>
-      <c r="AQ355" s="36"/>
-      <c r="AR355" s="36"/>
-      <c r="AS355" s="36"/>
-      <c r="AT355" s="36"/>
-      <c r="AU355" s="36"/>
-      <c r="AV355" s="36"/>
-      <c r="AW355" s="52"/>
-    </row>
-    <row r="356" customHeight="1" spans="1:49">
-      <c r="A356" s="35"/>
-      <c r="B356" s="36"/>
-      <c r="C356" s="36"/>
-      <c r="D356" s="36"/>
-      <c r="E356" s="36"/>
-      <c r="F356" s="36"/>
-      <c r="G356" s="36"/>
-      <c r="H356" s="36"/>
-      <c r="I356" s="36"/>
-      <c r="J356" s="36"/>
-      <c r="K356" s="36"/>
-      <c r="L356" s="36"/>
-      <c r="M356" s="36"/>
-      <c r="N356" s="36"/>
-      <c r="O356" s="36"/>
-      <c r="P356" s="36"/>
-      <c r="Q356" s="36"/>
-      <c r="R356" s="36"/>
-      <c r="S356" s="49"/>
-      <c r="T356" s="49"/>
-      <c r="U356" s="49"/>
-      <c r="V356" s="49"/>
-      <c r="W356" s="36"/>
-      <c r="X356" s="36"/>
-      <c r="Y356" s="36"/>
-      <c r="Z356" s="36"/>
-      <c r="AA356" s="36"/>
-      <c r="AB356" s="36"/>
-      <c r="AC356" s="36"/>
-      <c r="AD356" s="36"/>
-      <c r="AE356" s="36"/>
-      <c r="AF356" s="36"/>
-      <c r="AG356" s="36"/>
-      <c r="AH356" s="36"/>
-      <c r="AI356" s="36"/>
-      <c r="AJ356" s="36"/>
-      <c r="AK356" s="36"/>
-      <c r="AL356" s="36"/>
-      <c r="AM356" s="36"/>
-      <c r="AN356" s="36"/>
-      <c r="AO356" s="36"/>
-      <c r="AP356" s="36"/>
-      <c r="AQ356" s="36"/>
-      <c r="AR356" s="36"/>
-      <c r="AS356" s="36"/>
-      <c r="AT356" s="36"/>
-      <c r="AU356" s="36"/>
-      <c r="AV356" s="36"/>
-      <c r="AW356" s="52"/>
-    </row>
-    <row r="357" customHeight="1" spans="1:49">
-      <c r="A357" s="35"/>
-      <c r="B357" s="36"/>
-      <c r="C357" s="36"/>
-      <c r="D357" s="36"/>
-      <c r="E357" s="36"/>
-      <c r="F357" s="36"/>
-      <c r="G357" s="36"/>
-      <c r="H357" s="36"/>
-      <c r="I357" s="36"/>
-      <c r="J357" s="36"/>
-      <c r="K357" s="36"/>
-      <c r="L357" s="36"/>
-      <c r="M357" s="36"/>
-      <c r="N357" s="36"/>
-      <c r="O357" s="36"/>
-      <c r="P357" s="36"/>
-      <c r="Q357" s="36"/>
-      <c r="R357" s="36"/>
-      <c r="S357" s="49"/>
-      <c r="T357" s="49"/>
-      <c r="U357" s="49"/>
-      <c r="V357" s="49"/>
-      <c r="W357" s="36"/>
-      <c r="X357" s="36"/>
-      <c r="Y357" s="36"/>
-      <c r="Z357" s="36"/>
-      <c r="AA357" s="36"/>
-      <c r="AB357" s="36"/>
-      <c r="AC357" s="36"/>
-      <c r="AD357" s="36"/>
-      <c r="AE357" s="36"/>
-      <c r="AF357" s="36"/>
-      <c r="AG357" s="36"/>
-      <c r="AH357" s="36"/>
-      <c r="AI357" s="36"/>
-      <c r="AJ357" s="36"/>
-      <c r="AK357" s="36"/>
-      <c r="AL357" s="36"/>
-      <c r="AM357" s="36"/>
-      <c r="AN357" s="36"/>
-      <c r="AO357" s="36"/>
-      <c r="AP357" s="36"/>
-      <c r="AQ357" s="36"/>
-      <c r="AR357" s="36"/>
-      <c r="AS357" s="36"/>
-      <c r="AT357" s="36"/>
-      <c r="AU357" s="36"/>
-      <c r="AV357" s="36"/>
-      <c r="AW357" s="52"/>
-    </row>
-    <row r="358" customHeight="1" spans="1:49">
-      <c r="A358" s="35"/>
-      <c r="B358" s="36"/>
       <c r="C358" s="36"/>
       <c r="D358" s="36"/>
       <c r="E358" s="36"/>
@@ -13786,7 +19063,9 @@
     </row>
     <row r="359" customHeight="1" spans="1:49">
       <c r="A359" s="35"/>
-      <c r="B359" s="36"/>
+      <c r="B359" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="C359" s="36"/>
       <c r="D359" s="36"/>
       <c r="E359" s="36"/>
@@ -13836,69 +19115,262 @@
       <c r="AW359" s="52"/>
     </row>
     <row r="360" customHeight="1" spans="1:49">
-      <c r="A360" s="40"/>
-      <c r="B360" s="41"/>
-      <c r="C360" s="41"/>
-      <c r="D360" s="42"/>
-      <c r="E360" s="42"/>
-      <c r="F360" s="42"/>
-      <c r="G360" s="43"/>
-      <c r="H360" s="43"/>
-      <c r="I360" s="43"/>
-      <c r="AW360" s="54"/>
+      <c r="A360" s="35"/>
+      <c r="B360" s="36"/>
+      <c r="C360" s="36"/>
+      <c r="D360" s="36"/>
+      <c r="E360" s="36"/>
+      <c r="F360" s="36"/>
+      <c r="G360" s="36"/>
+      <c r="H360" s="36"/>
+      <c r="I360" s="36"/>
+      <c r="J360" s="36"/>
+      <c r="K360" s="36"/>
+      <c r="L360" s="36"/>
+      <c r="M360" s="36"/>
+      <c r="N360" s="36"/>
+      <c r="O360" s="36"/>
+      <c r="P360" s="36"/>
+      <c r="Q360" s="36"/>
+      <c r="R360" s="36"/>
+      <c r="S360" s="49"/>
+      <c r="T360" s="49"/>
+      <c r="U360" s="49"/>
+      <c r="V360" s="49"/>
+      <c r="W360" s="36"/>
+      <c r="X360" s="36"/>
+      <c r="Y360" s="36"/>
+      <c r="Z360" s="36"/>
+      <c r="AA360" s="36"/>
+      <c r="AB360" s="36"/>
+      <c r="AC360" s="36"/>
+      <c r="AD360" s="36"/>
+      <c r="AE360" s="36"/>
+      <c r="AF360" s="36"/>
+      <c r="AG360" s="36"/>
+      <c r="AH360" s="36"/>
+      <c r="AI360" s="36"/>
+      <c r="AJ360" s="36"/>
+      <c r="AK360" s="36"/>
+      <c r="AL360" s="36"/>
+      <c r="AM360" s="36"/>
+      <c r="AN360" s="36"/>
+      <c r="AO360" s="36"/>
+      <c r="AP360" s="36"/>
+      <c r="AQ360" s="36"/>
+      <c r="AR360" s="36"/>
+      <c r="AS360" s="36"/>
+      <c r="AT360" s="36"/>
+      <c r="AU360" s="36"/>
+      <c r="AV360" s="36"/>
+      <c r="AW360" s="52"/>
     </row>
     <row r="361" customHeight="1" spans="1:49">
-      <c r="A361" s="56" t="s">
-        <v>79</v>
-      </c>
-      <c r="B361" s="41"/>
-      <c r="C361" s="41"/>
-      <c r="D361" s="42"/>
-      <c r="E361" s="42"/>
-      <c r="F361" s="42"/>
-      <c r="G361" s="43"/>
-      <c r="H361" s="43"/>
-      <c r="I361" s="43"/>
-      <c r="AW361" s="54"/>
+      <c r="A361" s="35"/>
+      <c r="B361" s="36"/>
+      <c r="C361" s="36"/>
+      <c r="D361" s="36"/>
+      <c r="E361" s="36"/>
+      <c r="F361" s="36"/>
+      <c r="G361" s="36"/>
+      <c r="H361" s="36"/>
+      <c r="I361" s="36"/>
+      <c r="J361" s="36"/>
+      <c r="K361" s="36"/>
+      <c r="L361" s="36"/>
+      <c r="M361" s="36"/>
+      <c r="N361" s="36"/>
+      <c r="O361" s="36"/>
+      <c r="P361" s="36"/>
+      <c r="Q361" s="36"/>
+      <c r="R361" s="36"/>
+      <c r="S361" s="49"/>
+      <c r="T361" s="49"/>
+      <c r="U361" s="49"/>
+      <c r="V361" s="49"/>
+      <c r="W361" s="36"/>
+      <c r="X361" s="36"/>
+      <c r="Y361" s="36"/>
+      <c r="Z361" s="36"/>
+      <c r="AA361" s="36"/>
+      <c r="AB361" s="36"/>
+      <c r="AC361" s="36"/>
+      <c r="AD361" s="36"/>
+      <c r="AE361" s="36"/>
+      <c r="AF361" s="36"/>
+      <c r="AG361" s="36"/>
+      <c r="AH361" s="36"/>
+      <c r="AI361" s="36"/>
+      <c r="AJ361" s="36"/>
+      <c r="AK361" s="36"/>
+      <c r="AL361" s="36"/>
+      <c r="AM361" s="36"/>
+      <c r="AN361" s="36"/>
+      <c r="AO361" s="36"/>
+      <c r="AP361" s="36"/>
+      <c r="AQ361" s="36"/>
+      <c r="AR361" s="36"/>
+      <c r="AS361" s="36"/>
+      <c r="AT361" s="36"/>
+      <c r="AU361" s="36"/>
+      <c r="AV361" s="36"/>
+      <c r="AW361" s="52"/>
     </row>
     <row r="362" customHeight="1" spans="1:49">
-      <c r="A362" s="56"/>
-      <c r="B362" s="41"/>
-      <c r="C362" s="41"/>
-      <c r="D362" s="42"/>
-      <c r="E362" s="42"/>
-      <c r="F362" s="42"/>
-      <c r="G362" s="43"/>
-      <c r="H362" s="43"/>
-      <c r="I362" s="43"/>
-      <c r="AW362" s="54"/>
+      <c r="A362" s="35"/>
+      <c r="B362" s="36"/>
+      <c r="C362" s="36"/>
+      <c r="D362" s="36"/>
+      <c r="E362" s="36"/>
+      <c r="F362" s="36"/>
+      <c r="G362" s="36"/>
+      <c r="H362" s="36"/>
+      <c r="I362" s="36"/>
+      <c r="J362" s="36"/>
+      <c r="K362" s="36"/>
+      <c r="L362" s="36"/>
+      <c r="M362" s="36"/>
+      <c r="N362" s="36"/>
+      <c r="O362" s="36"/>
+      <c r="P362" s="36"/>
+      <c r="Q362" s="36"/>
+      <c r="R362" s="36"/>
+      <c r="S362" s="49"/>
+      <c r="T362" s="49"/>
+      <c r="U362" s="49"/>
+      <c r="V362" s="49"/>
+      <c r="W362" s="36"/>
+      <c r="X362" s="36"/>
+      <c r="Y362" s="36"/>
+      <c r="Z362" s="36"/>
+      <c r="AA362" s="36"/>
+      <c r="AB362" s="36"/>
+      <c r="AC362" s="36"/>
+      <c r="AD362" s="36"/>
+      <c r="AE362" s="36"/>
+      <c r="AF362" s="36"/>
+      <c r="AG362" s="36"/>
+      <c r="AH362" s="36"/>
+      <c r="AI362" s="36"/>
+      <c r="AJ362" s="36"/>
+      <c r="AK362" s="36"/>
+      <c r="AL362" s="36"/>
+      <c r="AM362" s="36"/>
+      <c r="AN362" s="36"/>
+      <c r="AO362" s="36"/>
+      <c r="AP362" s="36"/>
+      <c r="AQ362" s="36"/>
+      <c r="AR362" s="36"/>
+      <c r="AS362" s="36"/>
+      <c r="AT362" s="36"/>
+      <c r="AU362" s="36"/>
+      <c r="AV362" s="36"/>
+      <c r="AW362" s="52"/>
     </row>
     <row r="363" customHeight="1" spans="1:49">
-      <c r="A363" s="56"/>
-      <c r="B363" s="41"/>
-      <c r="C363" s="41"/>
-      <c r="D363" s="42"/>
-      <c r="E363" s="42"/>
-      <c r="F363" s="42"/>
-      <c r="G363" s="43"/>
-      <c r="H363" s="43"/>
-      <c r="I363" s="43"/>
-      <c r="AW363" s="54"/>
+      <c r="A363" s="35"/>
+      <c r="B363" s="36"/>
+      <c r="C363" s="36"/>
+      <c r="D363" s="36"/>
+      <c r="E363" s="36"/>
+      <c r="F363" s="36"/>
+      <c r="G363" s="36"/>
+      <c r="H363" s="36"/>
+      <c r="I363" s="36"/>
+      <c r="J363" s="36"/>
+      <c r="K363" s="36"/>
+      <c r="L363" s="36"/>
+      <c r="M363" s="36"/>
+      <c r="N363" s="36"/>
+      <c r="O363" s="36"/>
+      <c r="P363" s="36"/>
+      <c r="Q363" s="36"/>
+      <c r="R363" s="36"/>
+      <c r="S363" s="49"/>
+      <c r="T363" s="49"/>
+      <c r="U363" s="49"/>
+      <c r="V363" s="49"/>
+      <c r="W363" s="36"/>
+      <c r="X363" s="36"/>
+      <c r="Y363" s="36"/>
+      <c r="Z363" s="36"/>
+      <c r="AA363" s="36"/>
+      <c r="AB363" s="36"/>
+      <c r="AC363" s="36"/>
+      <c r="AD363" s="36"/>
+      <c r="AE363" s="36"/>
+      <c r="AF363" s="36"/>
+      <c r="AG363" s="36"/>
+      <c r="AH363" s="36"/>
+      <c r="AI363" s="36"/>
+      <c r="AJ363" s="36"/>
+      <c r="AK363" s="36"/>
+      <c r="AL363" s="36"/>
+      <c r="AM363" s="36"/>
+      <c r="AN363" s="36"/>
+      <c r="AO363" s="36"/>
+      <c r="AP363" s="36"/>
+      <c r="AQ363" s="36"/>
+      <c r="AR363" s="36"/>
+      <c r="AS363" s="36"/>
+      <c r="AT363" s="36"/>
+      <c r="AU363" s="36"/>
+      <c r="AV363" s="36"/>
+      <c r="AW363" s="52"/>
     </row>
     <row r="364" customHeight="1" spans="1:49">
-      <c r="A364" s="56"/>
-      <c r="B364" s="41"/>
-      <c r="C364" s="41"/>
-      <c r="D364" s="42"/>
-      <c r="E364" s="42"/>
-      <c r="F364" s="42"/>
-      <c r="G364" s="43"/>
-      <c r="H364" s="43"/>
-      <c r="I364" s="43"/>
-      <c r="AW364" s="54"/>
+      <c r="A364" s="35"/>
+      <c r="B364" s="36"/>
+      <c r="C364" s="36"/>
+      <c r="D364" s="36"/>
+      <c r="E364" s="36"/>
+      <c r="F364" s="36"/>
+      <c r="G364" s="36"/>
+      <c r="H364" s="36"/>
+      <c r="I364" s="36"/>
+      <c r="J364" s="36"/>
+      <c r="K364" s="36"/>
+      <c r="L364" s="36"/>
+      <c r="M364" s="36"/>
+      <c r="N364" s="36"/>
+      <c r="O364" s="36"/>
+      <c r="P364" s="36"/>
+      <c r="Q364" s="36"/>
+      <c r="R364" s="36"/>
+      <c r="S364" s="49"/>
+      <c r="T364" s="49"/>
+      <c r="U364" s="49"/>
+      <c r="V364" s="49"/>
+      <c r="W364" s="36"/>
+      <c r="X364" s="36"/>
+      <c r="Y364" s="36"/>
+      <c r="Z364" s="36"/>
+      <c r="AA364" s="36"/>
+      <c r="AB364" s="36"/>
+      <c r="AC364" s="36"/>
+      <c r="AD364" s="36"/>
+      <c r="AE364" s="36"/>
+      <c r="AF364" s="36"/>
+      <c r="AG364" s="36"/>
+      <c r="AH364" s="36"/>
+      <c r="AI364" s="36"/>
+      <c r="AJ364" s="36"/>
+      <c r="AK364" s="36"/>
+      <c r="AL364" s="36"/>
+      <c r="AM364" s="36"/>
+      <c r="AN364" s="36"/>
+      <c r="AO364" s="36"/>
+      <c r="AP364" s="36"/>
+      <c r="AQ364" s="36"/>
+      <c r="AR364" s="36"/>
+      <c r="AS364" s="36"/>
+      <c r="AT364" s="36"/>
+      <c r="AU364" s="36"/>
+      <c r="AV364" s="36"/>
+      <c r="AW364" s="52"/>
     </row>
     <row r="365" customHeight="1" spans="1:49">
-      <c r="A365" s="56"/>
+      <c r="A365" s="40"/>
       <c r="B365" s="41"/>
       <c r="C365" s="41"/>
       <c r="D365" s="42"/>
@@ -13910,7 +19382,9 @@
       <c r="AW365" s="54"/>
     </row>
     <row r="366" customHeight="1" spans="1:49">
-      <c r="A366" s="56"/>
+      <c r="A366" s="56" t="s">
+        <v>79</v>
+      </c>
       <c r="B366" s="41"/>
       <c r="C366" s="41"/>
       <c r="D366" s="42"/>
@@ -13982,7 +19456,7 @@
       <c r="AW371" s="54"/>
     </row>
     <row r="372" customHeight="1" spans="1:49">
-      <c r="A372" s="40"/>
+      <c r="A372" s="56"/>
       <c r="B372" s="41"/>
       <c r="C372" s="41"/>
       <c r="D372" s="42"/>
@@ -13994,7 +19468,7 @@
       <c r="AW372" s="54"/>
     </row>
     <row r="373" customHeight="1" spans="1:49">
-      <c r="A373" s="40"/>
+      <c r="A373" s="56"/>
       <c r="B373" s="41"/>
       <c r="C373" s="41"/>
       <c r="D373" s="42"/>
@@ -14006,7 +19480,7 @@
       <c r="AW373" s="54"/>
     </row>
     <row r="374" customHeight="1" spans="1:49">
-      <c r="A374" s="40"/>
+      <c r="A374" s="56"/>
       <c r="B374" s="41"/>
       <c r="C374" s="41"/>
       <c r="D374" s="42"/>
@@ -14018,7 +19492,7 @@
       <c r="AW374" s="54"/>
     </row>
     <row r="375" customHeight="1" spans="1:49">
-      <c r="A375" s="40"/>
+      <c r="A375" s="56"/>
       <c r="B375" s="41"/>
       <c r="C375" s="41"/>
       <c r="D375" s="42"/>
@@ -14030,7 +19504,7 @@
       <c r="AW375" s="54"/>
     </row>
     <row r="376" customHeight="1" spans="1:49">
-      <c r="A376" s="40"/>
+      <c r="A376" s="56"/>
       <c r="B376" s="41"/>
       <c r="C376" s="41"/>
       <c r="D376" s="42"/>
@@ -14174,55 +19648,115 @@
       <c r="AW387" s="54"/>
     </row>
     <row r="388" customHeight="1" spans="1:49">
-      <c r="A388" s="57"/>
-      <c r="B388" s="58"/>
-      <c r="C388" s="58"/>
-      <c r="D388" s="58"/>
-      <c r="E388" s="58"/>
-      <c r="F388" s="58"/>
-      <c r="G388" s="58"/>
-      <c r="H388" s="58"/>
-      <c r="I388" s="58"/>
-      <c r="J388" s="58"/>
-      <c r="K388" s="58"/>
-      <c r="L388" s="58"/>
-      <c r="M388" s="58"/>
-      <c r="N388" s="58"/>
-      <c r="O388" s="58"/>
-      <c r="P388" s="58"/>
-      <c r="Q388" s="58"/>
-      <c r="R388" s="58"/>
-      <c r="S388" s="58"/>
-      <c r="T388" s="58"/>
-      <c r="U388" s="58"/>
-      <c r="V388" s="58"/>
-      <c r="W388" s="58"/>
-      <c r="X388" s="58"/>
-      <c r="Y388" s="58"/>
-      <c r="Z388" s="58"/>
-      <c r="AA388" s="58"/>
-      <c r="AB388" s="58"/>
-      <c r="AC388" s="58"/>
-      <c r="AD388" s="58"/>
-      <c r="AE388" s="58"/>
-      <c r="AF388" s="58"/>
-      <c r="AG388" s="58"/>
-      <c r="AH388" s="58"/>
-      <c r="AI388" s="58"/>
-      <c r="AJ388" s="58"/>
-      <c r="AK388" s="58"/>
-      <c r="AL388" s="58"/>
-      <c r="AM388" s="58"/>
-      <c r="AN388" s="58"/>
-      <c r="AO388" s="58"/>
-      <c r="AP388" s="58"/>
-      <c r="AQ388" s="58"/>
-      <c r="AR388" s="58"/>
-      <c r="AS388" s="58"/>
-      <c r="AT388" s="58"/>
-      <c r="AU388" s="58"/>
-      <c r="AV388" s="58"/>
-      <c r="AW388" s="59"/>
+      <c r="A388" s="40"/>
+      <c r="B388" s="41"/>
+      <c r="C388" s="41"/>
+      <c r="D388" s="42"/>
+      <c r="E388" s="42"/>
+      <c r="F388" s="42"/>
+      <c r="G388" s="43"/>
+      <c r="H388" s="43"/>
+      <c r="I388" s="43"/>
+      <c r="AW388" s="54"/>
+    </row>
+    <row r="389" customHeight="1" spans="1:49">
+      <c r="A389" s="40"/>
+      <c r="B389" s="41"/>
+      <c r="C389" s="41"/>
+      <c r="D389" s="42"/>
+      <c r="E389" s="42"/>
+      <c r="F389" s="42"/>
+      <c r="G389" s="43"/>
+      <c r="H389" s="43"/>
+      <c r="I389" s="43"/>
+      <c r="AW389" s="54"/>
+    </row>
+    <row r="390" customHeight="1" spans="1:49">
+      <c r="A390" s="40"/>
+      <c r="B390" s="41"/>
+      <c r="C390" s="41"/>
+      <c r="D390" s="42"/>
+      <c r="E390" s="42"/>
+      <c r="F390" s="42"/>
+      <c r="G390" s="43"/>
+      <c r="H390" s="43"/>
+      <c r="I390" s="43"/>
+      <c r="AW390" s="54"/>
+    </row>
+    <row r="391" customHeight="1" spans="1:49">
+      <c r="A391" s="40"/>
+      <c r="B391" s="41"/>
+      <c r="C391" s="41"/>
+      <c r="D391" s="42"/>
+      <c r="E391" s="42"/>
+      <c r="F391" s="42"/>
+      <c r="G391" s="43"/>
+      <c r="H391" s="43"/>
+      <c r="I391" s="43"/>
+      <c r="AW391" s="54"/>
+    </row>
+    <row r="392" customHeight="1" spans="1:49">
+      <c r="A392" s="40"/>
+      <c r="B392" s="41"/>
+      <c r="C392" s="41"/>
+      <c r="D392" s="42"/>
+      <c r="E392" s="42"/>
+      <c r="F392" s="42"/>
+      <c r="G392" s="43"/>
+      <c r="H392" s="43"/>
+      <c r="I392" s="43"/>
+      <c r="AW392" s="54"/>
+    </row>
+    <row r="393" customHeight="1" spans="1:49">
+      <c r="A393" s="57"/>
+      <c r="B393" s="58"/>
+      <c r="C393" s="58"/>
+      <c r="D393" s="58"/>
+      <c r="E393" s="58"/>
+      <c r="F393" s="58"/>
+      <c r="G393" s="58"/>
+      <c r="H393" s="58"/>
+      <c r="I393" s="58"/>
+      <c r="J393" s="58"/>
+      <c r="K393" s="58"/>
+      <c r="L393" s="58"/>
+      <c r="M393" s="58"/>
+      <c r="N393" s="58"/>
+      <c r="O393" s="58"/>
+      <c r="P393" s="58"/>
+      <c r="Q393" s="58"/>
+      <c r="R393" s="58"/>
+      <c r="S393" s="58"/>
+      <c r="T393" s="58"/>
+      <c r="U393" s="58"/>
+      <c r="V393" s="58"/>
+      <c r="W393" s="58"/>
+      <c r="X393" s="58"/>
+      <c r="Y393" s="58"/>
+      <c r="Z393" s="58"/>
+      <c r="AA393" s="58"/>
+      <c r="AB393" s="58"/>
+      <c r="AC393" s="58"/>
+      <c r="AD393" s="58"/>
+      <c r="AE393" s="58"/>
+      <c r="AF393" s="58"/>
+      <c r="AG393" s="58"/>
+      <c r="AH393" s="58"/>
+      <c r="AI393" s="58"/>
+      <c r="AJ393" s="58"/>
+      <c r="AK393" s="58"/>
+      <c r="AL393" s="58"/>
+      <c r="AM393" s="58"/>
+      <c r="AN393" s="58"/>
+      <c r="AO393" s="58"/>
+      <c r="AP393" s="58"/>
+      <c r="AQ393" s="58"/>
+      <c r="AR393" s="58"/>
+      <c r="AS393" s="58"/>
+      <c r="AT393" s="58"/>
+      <c r="AU393" s="58"/>
+      <c r="AV393" s="58"/>
+      <c r="AW393" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -14248,8 +19782,8 @@
     <mergeCell ref="D275:F275"/>
     <mergeCell ref="A315:C315"/>
     <mergeCell ref="D315:F315"/>
-    <mergeCell ref="A351:C351"/>
-    <mergeCell ref="D351:F351"/>
+    <mergeCell ref="A356:C356"/>
+    <mergeCell ref="D356:F356"/>
     <mergeCell ref="A1:N4"/>
     <mergeCell ref="AB1:AD2"/>
     <mergeCell ref="AE1:AH2"/>
